--- a/web_summit_2026_participants.xlsx
+++ b/web_summit_2026_participants.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web Summit 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Web Summit 2026'!$A$1:$D$382</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Web Summit 2026'!$A$1:$F$382</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,13 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D382"/>
+  <dimension ref="A1:F382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +457,16 @@
           <t>Посада</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Тип учасника</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Країна</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,6 +487,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -495,6 +517,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -515,6 +547,16 @@
           <t>Co-Founder, CBDO</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -535,6 +577,16 @@
           <t>Co-founder, CEO</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -555,6 +607,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -575,6 +637,16 @@
           <t>Chief Technology Officer</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -595,6 +667,16 @@
           <t>Chief People Officer</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -615,6 +697,16 @@
           <t>Events Planning Coordinator</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -635,6 +727,16 @@
           <t>Marketing manager</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -655,6 +757,16 @@
           <t>Art director</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -675,6 +787,16 @@
           <t>Security Engineer</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -695,6 +817,16 @@
           <t>Strategy &amp; Business Operations Manager</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -715,6 +847,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -735,6 +877,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -755,6 +907,16 @@
           <t>TL Talent S&amp;D Manager</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -775,6 +937,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -795,6 +967,16 @@
           <t>Founding manager</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -815,6 +997,16 @@
           <t>AEM Developer</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -835,6 +1027,16 @@
           <t>Project manager</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -855,6 +1057,16 @@
           <t>Head of Partnerships</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -875,6 +1087,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -895,6 +1117,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -915,6 +1147,16 @@
           <t>Lead Machine Learning Engineer</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -935,6 +1177,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -955,6 +1207,16 @@
           <t>Software Test Automation Engineer</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -975,6 +1237,16 @@
           <t>Engineering Manager</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -995,6 +1267,16 @@
           <t>AI automation engineer</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1015,6 +1297,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1035,6 +1327,16 @@
           <t>Head of Robotics Platform</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1055,6 +1357,16 @@
           <t>CISO</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1075,6 +1387,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1095,6 +1417,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1115,6 +1447,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1135,6 +1477,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1155,6 +1507,16 @@
           <t>CFO</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1175,6 +1537,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1195,6 +1567,16 @@
           <t>Co-founder, CMO &amp; CBDO</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1215,6 +1597,16 @@
           <t>B2B Marketing Manager</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1235,6 +1627,16 @@
           <t>AEM Content Author</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1255,6 +1657,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1275,6 +1687,16 @@
           <t>Team Leader</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1295,6 +1717,16 @@
           <t>Co-Founder &amp; Chief Technology Officer</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1315,6 +1747,16 @@
           <t>Web developer</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1335,6 +1777,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1355,6 +1807,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1375,6 +1837,16 @@
           <t>Product Marketing manager</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1395,6 +1867,16 @@
           <t>Business Analyst</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1415,6 +1897,16 @@
           <t>Director, Account management</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1435,6 +1927,16 @@
           <t>Head of RnD</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1455,6 +1957,16 @@
           <t>Sales Director</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1475,6 +1987,16 @@
           <t>Co-founder &amp; CEO</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1495,6 +2017,16 @@
           <t>Co-founder and CTO</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1515,6 +2047,16 @@
           <t>GTM Engineer</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1535,6 +2077,16 @@
           <t>Teach lead</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1555,6 +2107,16 @@
           <t>Frontend lead (React+React Native)</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1575,6 +2137,16 @@
           <t>CRO</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1595,6 +2167,16 @@
           <t>Backend Developer</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1615,6 +2197,16 @@
           <t>Product Lead</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1635,6 +2227,16 @@
           <t>SEO Specialist</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1655,6 +2257,16 @@
           <t>co-founder</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1675,6 +2287,16 @@
           <t>Content Marketing Lead</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1695,6 +2317,16 @@
           <t>AI Developer</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1715,6 +2347,16 @@
           <t>Customer Acquisition Manager</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1735,6 +2377,16 @@
           <t>Co-founder &amp; Co-owner</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1755,6 +2407,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1775,6 +2437,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1795,6 +2467,16 @@
           <t>Head of LinkedIn Department</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1815,6 +2497,16 @@
           <t>Principal</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1835,6 +2527,16 @@
           <t>Delivery Manager</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1855,6 +2557,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1875,6 +2587,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1895,6 +2617,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1915,6 +2647,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1935,6 +2677,16 @@
           <t>Co-owner &amp; Strategic Advisor</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1955,6 +2707,16 @@
           <t>Investor</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1975,6 +2737,16 @@
           <t>SEO</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1995,6 +2767,16 @@
           <t>Engineer</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2015,6 +2797,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2035,6 +2827,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2055,6 +2857,16 @@
           <t>Vice-President</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2075,6 +2887,16 @@
           <t>CPTO</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2095,6 +2917,16 @@
           <t>Product Manager</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2115,6 +2947,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2135,6 +2977,16 @@
           <t>CTO, Solution Architect</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2155,6 +3007,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2175,6 +3037,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2195,6 +3067,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2215,6 +3097,16 @@
           <t>Product owner</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2235,6 +3127,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2255,6 +3157,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2275,6 +3187,16 @@
           <t>Inspector</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2295,6 +3217,16 @@
           <t>Product Manager</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2315,6 +3247,16 @@
           <t>CEO &amp; Founder</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2335,6 +3277,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2355,6 +3307,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2375,6 +3337,16 @@
           <t>Principal Software Engineer</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2395,6 +3367,16 @@
           <t>Chief Corporate &amp; SME Business Officer</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2415,6 +3397,16 @@
           <t>Business Analyst</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2435,6 +3427,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2455,6 +3457,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2475,6 +3487,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2495,6 +3517,16 @@
           <t>Head of Product</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2515,6 +3547,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2535,6 +3577,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2555,6 +3607,16 @@
           <t>Strategic Partnerships Manager</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2575,6 +3637,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2595,6 +3667,16 @@
           <t>COO and Co-Founder</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2615,6 +3697,16 @@
           <t>Product Designer</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2635,6 +3727,16 @@
           <t>FOUNDER CEO</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2655,6 +3757,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2675,6 +3787,16 @@
           <t>Principal Java Engineer</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2695,6 +3817,16 @@
           <t>Head of Product</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2715,6 +3847,16 @@
           <t>PM Competency Manager</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2735,6 +3877,16 @@
           <t>Co-Founder/COO</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2755,6 +3907,16 @@
           <t>Senior SEO Content Writer</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2775,6 +3937,16 @@
           <t>Founder &amp; CEO</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2795,6 +3967,16 @@
           <t>Tech lead/ai engineer</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2815,6 +3997,16 @@
           <t>Business Generalist</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2835,6 +4027,16 @@
           <t>PDM</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2855,6 +4057,16 @@
           <t>Operations manager</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2875,6 +4087,16 @@
           <t>Founder (BECOME), co-founder (FormSniper)</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2895,6 +4117,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2915,6 +4147,16 @@
           <t>Chief Marketing Officer</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2935,6 +4177,16 @@
           <t>HR / Operations Specialist</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2955,6 +4207,16 @@
           <t>Sales Department Representative</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2975,6 +4237,16 @@
           <t>Business Development</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2995,6 +4267,16 @@
           <t>SFE Manager</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3015,6 +4297,16 @@
           <t>Owner</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3035,6 +4327,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3055,6 +4357,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3075,6 +4387,16 @@
           <t>Frontend Mentor</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3095,6 +4417,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3115,6 +4447,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3135,6 +4477,16 @@
           <t>Mobile product designer</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3155,6 +4507,16 @@
           <t>University representative</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3175,6 +4537,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3195,6 +4567,16 @@
           <t>CEO&amp;Founder</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3215,6 +4597,16 @@
           <t>Business analyst</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3235,6 +4627,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3255,6 +4657,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3275,6 +4687,16 @@
           <t>Investor</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3295,6 +4717,16 @@
           <t>Co-Founder</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3315,6 +4747,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3335,6 +4777,16 @@
           <t>CHRO</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3355,6 +4807,16 @@
           <t>Business Development Manager</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3375,6 +4837,16 @@
           <t>VP of Engineering</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3395,6 +4867,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3415,6 +4897,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3435,6 +4927,16 @@
           <t>Payments manager</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3455,6 +4957,16 @@
           <t>Product designer</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3475,6 +4987,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3495,6 +5017,16 @@
           <t>Content Manager</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3515,6 +5047,16 @@
           <t>Design Quality Assurance</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3535,6 +5077,16 @@
           <t>Global Partnerships Acquisition</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3555,6 +5107,16 @@
           <t>Product /Brand Designer</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3575,6 +5137,16 @@
           <t>C&amp;B Specialist</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3595,6 +5167,16 @@
           <t>Digital officer</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3615,6 +5197,16 @@
           <t>Communications expert, CMO</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3635,6 +5227,16 @@
           <t>Senior Director</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3655,6 +5257,16 @@
           <t>Cybersecurity Engineer / Cloud &amp; Network Security Specialist</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3675,6 +5287,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3695,6 +5317,16 @@
           <t>CCO</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3715,6 +5347,16 @@
           <t>Global travel specialist</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3735,6 +5377,16 @@
           <t>DevOps Engineer</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3755,6 +5407,16 @@
           <t>Head of Operations</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3775,6 +5437,16 @@
           <t>CRO</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3795,6 +5467,16 @@
           <t>Product designer</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3815,6 +5497,16 @@
           <t>Business Development Manager</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3835,6 +5527,16 @@
           <t>Businesses Development Specialist</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3855,6 +5557,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3875,6 +5587,16 @@
           <t>Project Manager</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3895,6 +5617,16 @@
           <t>BDM</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3915,6 +5647,16 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3935,6 +5677,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3955,6 +5707,16 @@
           <t>QA Tech Lead</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3975,6 +5737,16 @@
           <t>Head of Growth</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3995,6 +5767,16 @@
           <t>Founder &amp; Creative Director</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4015,6 +5797,16 @@
           <t>Founder &amp; CEO</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4035,6 +5827,16 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4055,6 +5857,16 @@
           <t>Creative Director</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4075,6 +5887,16 @@
           <t>PDO Manager</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4095,6 +5917,16 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4115,6 +5947,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4135,6 +5977,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4155,6 +6007,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4175,6 +6037,16 @@
           <t>Head of Delivery</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4195,6 +6067,16 @@
           <t>IT</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4215,6 +6097,16 @@
           <t>Marketing Director</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4235,6 +6127,16 @@
           <t>Head of Acceleration Program</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4255,6 +6157,16 @@
           <t>SEO specialist</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4275,6 +6187,16 @@
           <t>Marketing Consultant</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4295,6 +6217,16 @@
           <t>Senior data analyst</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4315,6 +6247,16 @@
           <t>HR Specialist</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4335,6 +6277,16 @@
           <t>Senior AP accountant</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4355,6 +6307,16 @@
           <t>Senior Frontend Engineer</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4375,6 +6337,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4395,6 +6367,16 @@
           <t>Chief Commercial Officer</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Speaker</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4415,6 +6397,16 @@
           <t>Delivery manager</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4435,6 +6427,16 @@
           <t>Executive Director</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4455,6 +6457,16 @@
           <t>CEO &amp; Co-founder</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4475,6 +6487,16 @@
           <t>Title</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4495,6 +6517,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4515,6 +6547,16 @@
           <t>Junior Frontend</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4535,6 +6577,16 @@
           <t>Co-founder &amp; COO</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4555,6 +6607,16 @@
           <t>user</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4575,6 +6637,16 @@
           <t>Marketing and Brand Manager</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4595,6 +6667,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4615,6 +6697,16 @@
           <t>Technical Advisor</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4635,6 +6727,16 @@
           <t>Business Analyst / Product Manager</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4655,6 +6757,16 @@
           <t>Communication Director</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4675,6 +6787,16 @@
           <t>Delivery Manager</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4695,6 +6817,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4715,6 +6847,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4735,6 +6877,16 @@
           <t>Full-Stack Developer</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4755,6 +6907,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -4775,6 +6937,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -4795,6 +6967,16 @@
           <t>Creative Director</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -4815,6 +6997,16 @@
           <t>Principal Full-Stack Engineer</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -4835,6 +7027,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4855,6 +7057,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4875,6 +7087,16 @@
           <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4895,6 +7117,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4915,6 +7147,16 @@
           <t>CFO</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4935,6 +7177,16 @@
           <t>Self-employed – independent projects</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4955,6 +7207,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4975,6 +7237,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4995,6 +7267,16 @@
           <t>Director of Digital Technology Department</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5015,6 +7297,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5035,6 +7327,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5055,6 +7357,16 @@
           <t>Software developer</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5075,6 +7387,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5095,6 +7417,16 @@
           <t>Business Development Manager</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5115,6 +7447,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5135,6 +7477,16 @@
           <t>Owner</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5155,6 +7507,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5175,6 +7537,16 @@
           <t>Data Science Analyst</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5195,6 +7567,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5215,6 +7597,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5235,6 +7627,16 @@
           <t>Senior Fullstack Developer</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5255,6 +7657,16 @@
           <t>Director of Engineering</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5275,6 +7687,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5295,6 +7717,16 @@
           <t>Head of PR</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5315,6 +7747,16 @@
           <t>Delivery Manager</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5335,6 +7777,16 @@
           <t>Ecommerce product</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5355,6 +7807,16 @@
           <t>Co-owner</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5375,6 +7837,16 @@
           <t>Head of Business Development</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5395,6 +7867,16 @@
           <t>Event Marketing Manager</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -5415,6 +7897,16 @@
           <t>Product Owner</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -5435,6 +7927,16 @@
           <t>Data Engineer</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -5455,6 +7957,16 @@
           <t>Digital Transformation &amp; Innovation Lead</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -5475,6 +7987,16 @@
           <t>Project manager</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -5495,6 +8017,16 @@
           <t>PR &amp; Comms</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -5515,6 +8047,16 @@
           <t>Product Manager</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -5535,6 +8077,16 @@
           <t>PM/QA</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -5555,6 +8107,16 @@
           <t>Content Manager</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -5575,6 +8137,16 @@
           <t>Partnership coordinator</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -5595,6 +8167,16 @@
           <t>Customer Success Manager</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -5615,6 +8197,16 @@
           <t>Product Strategy &amp; Crowth Lead</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -5635,6 +8227,16 @@
           <t>marketer</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -5655,6 +8257,16 @@
           <t>Senior marketing manager</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -5675,6 +8287,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -5695,6 +8317,16 @@
           <t>Project Management</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -5715,6 +8347,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -5735,6 +8377,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -5755,6 +8407,16 @@
           <t>Creative Marketing Director</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -5775,6 +8437,16 @@
           <t>IOS Developer</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -5795,6 +8467,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -5815,6 +8497,16 @@
           <t>Software Engineer/Architect</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -5835,6 +8527,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -5855,6 +8557,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Forum Guest</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -5875,6 +8587,16 @@
           <t>Product Owner</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -5895,6 +8617,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -5915,6 +8647,16 @@
           <t>Manager</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -5935,6 +8677,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -5955,6 +8707,16 @@
           <t>DM</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -5975,6 +8737,16 @@
           <t>Software Developer</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -5995,6 +8767,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6015,6 +8797,16 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6035,6 +8827,16 @@
           <t>COO</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6055,6 +8857,16 @@
           <t>Head of IT Depatrament</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6075,6 +8887,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6095,6 +8917,16 @@
           <t>CPO</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6115,6 +8947,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6135,6 +8977,16 @@
           <t>Business Operations Director</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -6155,6 +9007,16 @@
           <t>co-owner</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -6175,6 +9037,16 @@
           <t>Staff Engineer</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6195,6 +9067,16 @@
           <t>AI Creator</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6215,6 +9097,16 @@
           <t>SEO&amp;ASO Specialist</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6235,6 +9127,16 @@
           <t>Software engineer</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6255,6 +9157,16 @@
           <t>Intern</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6275,6 +9187,16 @@
           <t>Sales Manager</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6295,6 +9217,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -6315,6 +9247,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -6335,6 +9277,16 @@
           <t>AI dealer</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -6355,6 +9307,16 @@
           <t>Co-Founder</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -6375,6 +9337,16 @@
           <t>Account manager</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -6395,6 +9367,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -6415,6 +9397,16 @@
           <t>Founder &amp; marketer</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -6435,6 +9427,16 @@
           <t>Head of Product</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -6455,6 +9457,16 @@
           <t>Product Manager</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -6475,6 +9487,16 @@
           <t>Business Owner</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -6495,6 +9517,16 @@
           <t>Change manager, organizational coach</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -6515,6 +9547,16 @@
           <t>CIO/CDO</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -6535,6 +9577,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -6555,6 +9607,16 @@
           <t>Founder &amp; General Partner</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -6575,6 +9637,16 @@
           <t>Head of Sales</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -6595,6 +9667,16 @@
           <t>Marketing Manager</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -6615,6 +9697,16 @@
           <t>HR consultant</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -6635,6 +9727,16 @@
           <t>Partnerships executive</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -6655,6 +9757,16 @@
           <t>Marketing &amp; Partnerships Lead</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -6675,6 +9787,16 @@
           <t>Growth Marketer</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -6695,6 +9817,16 @@
           <t>Founder</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -6715,6 +9847,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -6735,6 +9877,16 @@
           <t>Software Engineer</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -6755,6 +9907,16 @@
           <t>Front End Engineer</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -6775,6 +9937,16 @@
           <t>Head of Recruitment</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -6795,6 +9967,16 @@
           <t>Product manager</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -6815,6 +9997,16 @@
           <t>SDR</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -6835,6 +10027,16 @@
           <t>Head of TD School</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -6855,6 +10057,16 @@
           <t>GTM &amp; Growth Solutions Lead</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -6875,6 +10087,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -6895,6 +10117,16 @@
           <t>Head of CA</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -6915,6 +10147,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -6935,6 +10177,16 @@
           <t>Community &amp; Partnership manager</t>
         </is>
       </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -6955,6 +10207,16 @@
           <t>Co-Founder</t>
         </is>
       </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -6975,6 +10237,16 @@
           <t>Head of innovations and digital development</t>
         </is>
       </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -6995,6 +10267,16 @@
           <t>Senior Software Engineer</t>
         </is>
       </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7015,6 +10297,16 @@
           <t>Sources</t>
         </is>
       </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7035,6 +10327,16 @@
           <t>Head of Marketing</t>
         </is>
       </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7055,6 +10357,16 @@
           <t>HRD</t>
         </is>
       </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7075,6 +10387,16 @@
           <t>HR Operations / L&amp;D Specialist</t>
         </is>
       </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7095,6 +10417,16 @@
           <t>HRBP</t>
         </is>
       </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7115,6 +10447,16 @@
           <t>Business Facilitator, Soft Skills and TEDx speaker coach</t>
         </is>
       </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7135,6 +10477,16 @@
           <t>Founder &amp; CEO</t>
         </is>
       </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7155,6 +10507,16 @@
           <t>Board Member</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7175,6 +10537,16 @@
           <t>SRE / DevOps / Infrastructure Engineer</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7195,6 +10567,16 @@
           <t>CMO</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -7215,6 +10597,16 @@
           <t>PM</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -7235,6 +10627,16 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -7255,6 +10657,16 @@
           <t>Head of Global Partnerships</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -7275,6 +10687,16 @@
           <t>Engineer</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -7295,6 +10717,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -7315,6 +10747,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -7335,6 +10777,16 @@
           <t>PO</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -7355,6 +10807,16 @@
           <t>Head of Department</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -7375,6 +10837,16 @@
           <t>International lawyer</t>
         </is>
       </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -7395,6 +10867,16 @@
           <t>AI Content</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -7415,6 +10897,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -7435,6 +10927,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -7455,6 +10957,16 @@
           <t>Lead Software Engineer</t>
         </is>
       </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -7475,6 +10987,16 @@
           <t>Front-end team leader</t>
         </is>
       </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -7495,6 +11017,16 @@
           <t>Marketing manager</t>
         </is>
       </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -7515,6 +11047,16 @@
           <t>Manager</t>
         </is>
       </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -7535,6 +11077,16 @@
           <t>CEO</t>
         </is>
       </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -7555,6 +11107,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -7575,6 +11137,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -7595,6 +11167,16 @@
           <t>Product manager</t>
         </is>
       </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -7615,6 +11197,16 @@
           <t>Co-founder</t>
         </is>
       </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -7635,6 +11227,16 @@
           <t>E-commerce Director</t>
         </is>
       </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -7655,6 +11257,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -7675,6 +11287,16 @@
           <t>Head PMM</t>
         </is>
       </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -7695,6 +11317,16 @@
           <t>CTO</t>
         </is>
       </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -7715,6 +11347,16 @@
           <t>Partner Success Manager</t>
         </is>
       </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -7735,6 +11377,16 @@
           <t>Web Devepoler</t>
         </is>
       </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -7755,6 +11407,16 @@
           <t>Developer</t>
         </is>
       </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -7775,6 +11437,16 @@
           <t>Enterprener</t>
         </is>
       </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -7795,6 +11467,16 @@
           <t>Chief Product Officer</t>
         </is>
       </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -7815,6 +11497,16 @@
           <t>Technical Lead</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -7835,6 +11527,16 @@
           <t>Technical Communicator</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -7855,6 +11557,16 @@
           <t>Software Developer</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -7875,6 +11587,16 @@
           <t>UI/UX Designer</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -7895,6 +11617,16 @@
           <t>Engagement Manager</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -7915,6 +11647,16 @@
           <t>Product Manager Mobile</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -7935,6 +11677,16 @@
           <t>Manual QA</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -7955,6 +11707,16 @@
           <t>Account Manager</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -7975,6 +11737,16 @@
           <t>Product manager/ Business consultant</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -7995,6 +11767,16 @@
           <t>Partner Manager</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Women in Tech</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -8015,6 +11797,16 @@
           <t>Product Manager</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -8035,6 +11827,16 @@
           <t>Co-Founder / CEO</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -8055,6 +11857,16 @@
           <t>Engineer</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -8075,9 +11887,19 @@
           <t>Senior software engineer</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Attendee</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D382"/>
+  <autoFilter ref="A1:F382"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>